--- a/factory/麦安研门店配货明细表_格式化模板.xlsx
+++ b/factory/麦安研门店配货明细表_格式化模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781F6D14-0677-4509-A751-D9C39A6A6211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14286509-BBD8-49AD-B048-6D8001AB1BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宝泰配货表" sheetId="2" r:id="rId1"/>
@@ -169,7 +169,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -201,9 +201,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -736,35 +733,35 @@
   <dimension ref="A1:XFC7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="4.21875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.88671875" style="20" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" style="20" customWidth="1"/>
-    <col min="9" max="9" width="6.21875" style="20" customWidth="1"/>
-    <col min="10" max="10" width="8.44140625" style="21" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="21" customWidth="1"/>
-    <col min="12" max="16383" width="9" style="14"/>
-    <col min="16384" max="16384" width="9" style="15"/>
+    <col min="1" max="1" width="19.33203125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="4.21875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" style="19" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" style="19" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" style="19" customWidth="1"/>
+    <col min="9" max="9" width="6.21875" style="19" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" style="20" customWidth="1"/>
+    <col min="11" max="11" width="9.77734375" style="20" customWidth="1"/>
+    <col min="12" max="16383" width="9" style="13"/>
+    <col min="16384" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16383" s="1" customFormat="1" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:16383" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -17174,14 +17171,14 @@
       <c r="XFC2" s="6"/>
     </row>
     <row r="3" spans="1:16383" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="7">
         <f>SUM(G4:G5)</f>
         <v>0</v>
@@ -33577,52 +33574,52 @@
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:16383" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
     </row>
     <row r="6" spans="1:16383" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="11"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:16383" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
